--- a/salon_forms/007_makeup_intake_form--salon_forms.xlsx
+++ b/salon_forms/007_makeup_intake_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>service_type_1</t>
+          <t>service type 1</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hair_type_1</t>
+          <t>hair type 1</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hair_type_2</t>
+          <t>hair type 2</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hair_type_3</t>
+          <t>hair type 3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>color_scheme_1</t>
+          <t>color scheme 1</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>color_scheme_2</t>
+          <t>color scheme 2</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>color_scheme_3</t>
+          <t>color scheme 3</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eye_color_1</t>
+          <t>eye color 1</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eye_color_2</t>
+          <t>eye color 2</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>eye_color_3</t>
+          <t>eye color 3</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lip_color_1</t>
+          <t>lip color 1</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lip_color_2</t>
+          <t>lip color 2</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lip_color_3</t>
+          <t>lip color 3</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>eye_brow_color_1</t>
+          <t>eye brow color 1</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eye_brow_color_2</t>
+          <t>eye brow color 2</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eye_brow_color_3</t>
+          <t>eye brow color 3</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>brow_type_1</t>
+          <t>brow type 1</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>brow_type_2</t>
+          <t>brow type 2</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>brow_type_3</t>
+          <t>brow type 3</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>brow_style_1</t>
+          <t>brow style 1</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>brow_style_2</t>
+          <t>brow style 2</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>brow_style_3</t>
+          <t>brow style 3</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>make_up_style_1</t>
+          <t>make up style 1</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>make_up_style_2</t>
+          <t>make up style 2</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>make_up_style_3</t>
+          <t>make up style 3</t>
         </is>
       </c>
     </row>
